--- a/instance/tournament_2_schedule.xlsx
+++ b/instance/tournament_2_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -789,17 +789,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Janice Lee</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -882,22 +882,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Yijun Liu</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -916,102 +916,110 @@
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Haocheng Teng</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Shan Zhong</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Ryuto Leegomonchai</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1034,22 +1042,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Edward Wang</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Vincent Onggoputra</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Edward Wang</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1087,22 +1095,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1140,22 +1148,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1173,53 +1181,57 @@
       <c r="M14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee / Cindy Lim</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Zain Merchant</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1242,17 +1254,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1296,12 +1308,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1345,12 +1357,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Meghan Wong / Makenna Wong</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1379,32 +1391,32 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Yifei Zheng, Juncheng Tang</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1447,17 +1459,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Manmeeth Nagesh, Jason Liu</t>
+          <t>Manmeeth Nagesh, Jason Liu</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1495,22 +1507,22 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Heng Wu, Haonan Wang, Avi Aswal, Aryan Khandekar</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1543,7 +1555,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1553,17 +1565,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Reyna Wan, Elisa Liu</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1581,53 +1593,57 @@
       <c r="M22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Court 4</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh, Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1645,27 +1661,27 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Yen Zhen Tan, Sirui Jiang</t>
+          <t>Juncheng Tang, Yifei Zheng, Jason Liu</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1698,7 +1714,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1708,17 +1724,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Elisa Liu, Reyna Wan</t>
+          <t>Heng Wu, Jason Liu, Aryan Khandekar</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1761,17 +1777,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Haonan Wang, Manmeeth Nagesh, Avi Aswal</t>
+          <t>Prathamesh Koranne, Yifei Zheng, Manmeeth Nagesh, Juncheng Tang</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1789,163 +1805,151 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Yuhung Kung / Jason Liu</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Yuhung Kung, Yifei Zheng, Jason Liu, Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 4</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Edward Wang / Dominic Pang</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Wenhao Zhang, Dominic Pang, Edward Wang, Yingchao Peng</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Court 4</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Hancheng Li, Zhuoran Cheng, Brandon Pham, Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1958,12 +1962,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1973,12 +1977,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #2</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2017,17 +2021,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #3</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #4</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2045,738 +2049,210 @@
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #3</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #4</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total Affected Players</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #3</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #4</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Court 3</t>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Court 4</t>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Court 5</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
-      <c r="M45" s="4" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Total Affected Players</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="n">
-        <v>22</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Reyna Wan</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Elisa Liu</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 1 times</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Prathamesh Koranne</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Midy Tao</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Yen Zhen Tan</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Sirui Jiang</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Elisa Liu</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Reyna Wan</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Wenhao Zhang</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Yingchao Peng</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hancheng Li</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Zhuoran Cheng</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Brandon Pham</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>

--- a/instance/tournament_2_schedule.xlsx
+++ b/instance/tournament_2_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -598,12 +598,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Yantao Fang / Shiyang Chang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Zhuoran Cheng / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -818,53 +818,57 @@
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -877,12 +881,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -892,12 +896,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Martin Lee / Anais Molinaro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Jiayi Shi / Haipeng Huang</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -916,371 +920,351 @@
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Hanna Yun / Cynthia Liu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Janice Lee / Cindy Lim</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Ines Bocanegra</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Onggoputra</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Rishi Jain</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang, Avi Aswal</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Haocheng Teng</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Zain Merchant</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Yuhung Kung</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Ryuto Leegomonchai</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Martin Lee</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Haocheng Teng</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1293,12 +1277,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1308,12 +1292,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1332,106 +1316,106 @@
       <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Meghan Wong / Makenna Wong</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1464,12 +1448,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh, Jason Liu</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1487,110 +1471,102 @@
       <c r="M20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu, Haonan Wang, Avi Aswal, Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lee</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Reyna Wan, Elisa Liu</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Stephen Guan</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1618,17 +1594,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh, Haonan Wang, Avi Aswal</t>
+          <t>Avi Aswal, Haonan Wang</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1661,7 +1637,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1671,17 +1647,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Yifei Zheng, Jason Liu</t>
+          <t>Makenna Wong, Meghan Wong</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1724,17 +1700,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Jason Liu, Aryan Khandekar</t>
+          <t>Yuhung Kung, Jason Liu, Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1777,7 +1753,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1787,7 +1763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Yifei Zheng, Manmeeth Nagesh, Juncheng Tang</t>
+          <t>Avi Aswal, Juncheng Tang, Haonan Wang, Yifei Zheng</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1805,444 +1781,807 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan, Elisa Liu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal, Prathamesh Koranne, Haonan Wang, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung, Juncheng Tang, Yifei Zheng, Jason Liu</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan, Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Junjie Zhou / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Meghan Wong, Elisa Liu, Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung, Jason Liu</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Junjie Zhou / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan, Junjie Zhou, Yifei Zheng, Elisa Liu</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung, Yang Jiao, Meghan Wong, Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Juncheng Tang, Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 3</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 4</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 1</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 2</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 4</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Court 4</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Total Affected Players</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Heng Wu</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Reyna Wan</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="F47" t="inlineStr">
         <is>
-          <t>Elisa Liu</t>
+          <t>Yifei Zheng</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 5 times</t>
         </is>
       </c>
     </row>
@@ -2253,6 +2592,174 @@
         </is>
       </c>
       <c r="M48" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Meghan Wong</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Reyna Wan</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Elisa Liu</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Makenna Wong</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Junjie Zhou</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Yang Jiao</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>

--- a/instance/tournament_2_schedule.xlsx
+++ b/instance/tournament_2_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -740,17 +740,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Yantao Fang / Shiyang Chang</t>
+          <t>Shan Zhong / Fanghong Huang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Zhuoran Cheng / Yen Zhen Tan</t>
+          <t>Jiayi Shi / Haipeng Huang</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -779,27 +779,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne</t>
+          <t>Yifei Zheng</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -886,22 +886,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee / Anais Molinaro</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Jiayi Shi / Haipeng Huang</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -945,12 +945,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>Janice Lee / Cindy Lim</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>Hanna Yun / Cynthia Liu</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -984,22 +984,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Shiyang Chang</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1033,22 +1033,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Fanghong Huang</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1067,53 +1067,57 @@
       <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ryuto Leegomonchai</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1126,27 +1130,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Jean Luo / Ted Mao</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Zhuoran Cheng / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1195,7 +1199,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -1214,159 +1218,155 @@
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Brandon Pham</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Brandon Pham</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Ryuto Leegomonchai</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1418,57 +1418,53 @@
       <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1491,17 +1487,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1530,27 +1526,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1604,7 +1600,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Haonan Wang</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1705,12 +1701,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Jason Liu, Manmeeth Nagesh</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1753,7 +1749,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1763,7 +1759,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Juncheng Tang, Haonan Wang, Yifei Zheng</t>
+          <t>Yuhung Kung, Yifei Zheng, Juncheng Tang, Jason Liu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1864,12 +1860,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Prathamesh Koranne, Haonan Wang, Manmeeth Nagesh</t>
+          <t>Yuhung Kung, Prathamesh Koranne, Manmeeth Nagesh, Jason Liu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1912,7 +1908,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1922,7 +1918,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Juncheng Tang, Yifei Zheng, Jason Liu</t>
+          <t>Haonan Wang, Yifei Zheng, Avi Aswal, Juncheng Tang</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1955,7 +1951,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1965,17 +1961,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan / Yifei Zheng</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan, Yifei Zheng</t>
+          <t>Aryan Khandekar, Heng Wu, Prathamesh Koranne, Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -2018,17 +2014,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Junjie Zhou / Elisa Liu</t>
+          <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong, Elisa Liu, Prathamesh Koranne</t>
+          <t>Yifei Zheng, Elisa Liu, Reyna Wan</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2061,7 +2057,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2071,17 +2067,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Jason Liu</t>
+          <t>Junjie Zhou, Prathamesh Koranne, Elisa Liu</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2124,7 +2120,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Junjie Zhou / Elisa Liu</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2134,7 +2130,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan, Junjie Zhou, Yifei Zheng, Elisa Liu</t>
+          <t>Reyna Wan, Yifei Zheng, Bernice Tse Ling Tung</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2167,7 +2163,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2177,17 +2173,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung, Yang Jiao, Meghan Wong, Prathamesh Koranne</t>
+          <t>Aryan Khandekar, Heng Wu, Yuhung Kung, Jason Liu</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2230,17 +2226,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Yifei Zheng</t>
+          <t>Prathamesh Koranne, Bernice Tse Ling Tung</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2268,17 +2264,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2425,7 +2421,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2570,7 +2566,7 @@
       <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
@@ -2600,19 +2596,19 @@
     <row r="49">
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Consecutive 4 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="F50" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -2624,7 +2620,7 @@
     <row r="51">
       <c r="F51" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2636,7 +2632,7 @@
     <row r="52">
       <c r="F52" t="inlineStr">
         <is>
-          <t>Meghan Wong</t>
+          <t>Reyna Wan</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -2648,7 +2644,7 @@
     <row r="53">
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Elisa Liu</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -2660,12 +2656,12 @@
     <row r="54">
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Consecutive 3 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
@@ -2677,62 +2673,62 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Consecutive 3 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reyna Wan</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Consecutive 3 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elisa Liu</t>
+          <t>Aryan Khandekar</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Consecutive 3 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="F58" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Heng Wu</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="F59" t="inlineStr">
         <is>
-          <t>Makenna Wong</t>
+          <t>Bernice Tse Ling Tung</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="F60" t="inlineStr">
         <is>
-          <t>Junjie Zhou</t>
+          <t>Brandon Pham</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -2744,7 +2740,7 @@
     <row r="61">
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung</t>
+          <t>Makenna Wong</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -2756,10 +2752,22 @@
     <row r="62">
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yang Jiao</t>
+          <t>Meghan Wong</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Junjie Zhou</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>
